--- a/Project_12_Repeating/How to Approach ML Problems/How_to.xlsx
+++ b/Project_12_Repeating/How to Approach ML Problems/How_to.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24380" windowHeight="9020" activeTab="1"/>
+    <workbookView windowWidth="27480" windowHeight="10880" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ideas" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>IDEA</t>
   </si>
@@ -94,19 +94,47 @@
   </si>
   <si>
     <t>Details</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>https://github.com/McLight-Note/AI-self-study/tree/main/Project_12_Repeating/How%20to%20Approach%20ML%20Problems</t>
+  </si>
+  <si>
+    <t>Ridge</t>
+  </si>
+  <si>
+    <t>alpha = 0.6</t>
+  </si>
+  <si>
+    <t>Lasso</t>
+  </si>
+  <si>
+    <t>ElasticNet</t>
+  </si>
+  <si>
+    <t>SGDRegressor</t>
+  </si>
+  <si>
+    <t>DecisionTree</t>
+  </si>
+  <si>
+    <t>RandomForestRegressor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="mmm\-yy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +148,20 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="7"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -587,142 +629,154 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="9"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1334,14 +1388,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
+    <col min="1" max="1" width="22.9453125" customWidth="1"/>
     <col min="3" max="3" width="18.09375" customWidth="1"/>
     <col min="4" max="4" width="14.5625" customWidth="1"/>
     <col min="5" max="5" width="16.65625" customWidth="1"/>
     <col min="6" max="6" width="10.59375" customWidth="1"/>
-    <col min="7" max="7" width="13.671875" customWidth="1"/>
+    <col min="7" max="7" width="64" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1370,7 +1425,118 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>41609</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2741.58719191657</v>
+      </c>
+      <c r="E2" s="4">
+        <v>2817.77979401171</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2741.58719508144</v>
+      </c>
+      <c r="E3" s="4">
+        <v>2817.77846654095</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4"/>
+      <c r="D4" s="4">
+        <v>2741.71439046405</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2817.94729240452</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5"/>
+      <c r="D5" s="4">
+        <v>2879.04321039039</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2972.66588605033</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6"/>
+      <c r="D6" s="4">
+        <v>2742.10310078539</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2814.89926163673</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1559.73786004802</v>
+      </c>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="D8" s="4">
+        <v>474.919897466689</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1371.73219234699</v>
+      </c>
+      <c r="G8" s="5"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:B8"/>
+    <mergeCell ref="G2:G8"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://github.com/McLight-Note/AI-self-study/tree/main/Project_12_Repeating/How%20to%20Approach%20ML%20Problems"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
